--- a/artfynd/A 63145-2025 artfynd.xlsx
+++ b/artfynd/A 63145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126009986</v>
+        <v>95973039</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartmuren S, Vstm</t>
+          <t>Mantmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561403</v>
+        <v>562257</v>
       </c>
       <c r="R2" t="n">
-        <v>6633563</v>
+        <v>6632887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,85 +772,84 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog, inslag av löv</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126009937</v>
+        <v>67792845</v>
       </c>
       <c r="B3" t="n">
-        <v>100450</v>
+        <v>43426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>100942</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartmuren S, Vstm</t>
+          <t>Mantmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561413</v>
+        <v>562257</v>
       </c>
       <c r="R3" t="n">
-        <v>6633502</v>
+        <v>6632887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +876,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,34 +890,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Granskog, inslag av björk</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126009878</v>
+        <v>80887878</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,53 +923,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartmuren S, Vstm</t>
+          <t>Ulvsbomursvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561378</v>
+        <v>561733</v>
       </c>
       <c r="R4" t="n">
-        <v>6633545</v>
+        <v>6633301</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,12 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2019-11-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2019-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,85 +1008,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Granskog, inslag av björk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126010031</v>
+        <v>127502233</v>
       </c>
       <c r="B5" t="n">
-        <v>100450</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartmuren S, Vstm</t>
+          <t>Mantmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561447</v>
+        <v>562257</v>
       </c>
       <c r="R5" t="n">
-        <v>6633560</v>
+        <v>6632887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,12 +1107,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1k-fåglar som tiggde mat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,27 +1136,1093 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog gran, asp, björk</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126009135</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561326</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6633664</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogsduynge</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126009878</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartmuren S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561378</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6633545</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126009937</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartmuren S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561413</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6633502</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126009986</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartmuren S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561403</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6633563</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av löv</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126010004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartmuren S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>561408</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6633581</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av löv</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126010031</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartmuren S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>561447</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6633560</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blandskog gran, asp, björk</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126010125</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartmuren SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>561496</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6633625</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kanten på bäckravin mot gammal åkermark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126010165</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartmuren SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>561474</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633633</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Blockrik åkerholme</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126009108</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartmuren V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>561293</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6633645</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>+ blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63145-2025 artfynd.xlsx
+++ b/artfynd/A 63145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95973039</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67792845</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80887878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127502233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126009135</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126009878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1508,6 +1543,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126009937</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1627,6 +1667,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126009986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1746,6 +1791,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010004</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1865,6 +1915,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010031</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1984,6 +2039,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010125</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2103,6 +2163,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010165</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2223,8 +2288,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126009108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>